--- a/PG.Web/PG.Web/DownloadSample/sample_parcel_import.xlsx
+++ b/PG.Web/PG.Web/DownloadSample/sample_parcel_import.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mamun\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WRL_Source\WRL\PG.Web\PG.Web\DownloadSample\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="17256" windowHeight="5928"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="17260" windowHeight="5930"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,55 +19,109 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="14">
-  <si>
-    <t>John Doe</t>
-  </si>
-  <si>
-    <t>Jane Smith</t>
-  </si>
-  <si>
-    <t>123 Main St</t>
-  </si>
-  <si>
-    <t>456 Oak Rd</t>
-  </si>
-  <si>
-    <t>01700000001</t>
-  </si>
-  <si>
-    <t>01700000002</t>
-  </si>
-  <si>
-    <t>CONSIGNEE_NAME</t>
-  </si>
-  <si>
-    <t>CONSIGNEE_ADDRESS</t>
-  </si>
-  <si>
-    <t>CONSIGNEE_MOBILE_NO</t>
-  </si>
-  <si>
-    <t>DESTINATION_DIST_NAME</t>
-  </si>
-  <si>
-    <t>DESTINATION_TOWN_NAME</t>
-  </si>
-  <si>
-    <t>Dhaka</t>
-  </si>
-  <si>
-    <t>Mohakhali</t>
-  </si>
-  <si>
-    <t>Banani</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="32">
+  <si>
+    <t>SL_NO</t>
+  </si>
+  <si>
+    <t>PICKUP_DATE</t>
+  </si>
+  <si>
+    <t>CLIENT_CODE</t>
+  </si>
+  <si>
+    <t>NAME</t>
+  </si>
+  <si>
+    <t>MobileNo</t>
+  </si>
+  <si>
+    <t>Address</t>
+  </si>
+  <si>
+    <t>Item</t>
+  </si>
+  <si>
+    <t>Product_Type</t>
+  </si>
+  <si>
+    <t>UPS</t>
+  </si>
+  <si>
+    <t>Destination</t>
+  </si>
+  <si>
+    <t>SLA_Breeze</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Narration</t>
+  </si>
+  <si>
+    <t>REF_TYPE</t>
+  </si>
+  <si>
+    <t>12.03.2025</t>
+  </si>
+  <si>
+    <t>PP1000001</t>
+  </si>
+  <si>
+    <t>SAKIBUL ISLAM</t>
+  </si>
+  <si>
+    <t>63, KDA AVENUE ,KHULNA</t>
+  </si>
+  <si>
+    <t>Credit Card</t>
+  </si>
+  <si>
+    <t>Khulna-9000</t>
+  </si>
+  <si>
+    <t>test</t>
+  </si>
+  <si>
+    <t>REF</t>
+  </si>
+  <si>
+    <t>PP1000002</t>
+  </si>
+  <si>
+    <t>MD. TANVIR AHAMED</t>
+  </si>
+  <si>
+    <t>NOYANAGAR MOHILA MADRASA, KHILKHET, DHAK A-1229</t>
+  </si>
+  <si>
+    <t>Dhaka-1229</t>
+  </si>
+  <si>
+    <t>PP1000003</t>
+  </si>
+  <si>
+    <t>MONIRA</t>
+  </si>
+  <si>
+    <t>ZIGATOLA, TOLLABAG 18/4 A</t>
+  </si>
+  <si>
+    <t>Dhaka-1000</t>
+  </si>
+  <si>
+    <t>DISTANCE_TYPE</t>
+  </si>
+  <si>
+    <t>DHAKA</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -83,16 +137,41 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -115,14 +194,50 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -428,65 +543,181 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:O4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="17.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.54296875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="24" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="25.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="25.81640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.1796875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="L1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A2" s="6">
+        <v>1</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" s="7"/>
+      <c r="F2" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6">
+        <v>820000001</v>
+      </c>
+      <c r="J2" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" s="9">
+        <v>5</v>
+      </c>
+      <c r="L2" s="6"/>
+      <c r="M2" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="N2" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="O2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A3" s="6">
         <v>2</v>
       </c>
-      <c r="C2" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" t="s">
-        <v>12</v>
+      <c r="B3" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" s="7"/>
+      <c r="F3" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6">
+        <v>820000002</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="K3" s="9">
+        <v>5</v>
+      </c>
+      <c r="L3" s="6"/>
+      <c r="M3" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="N3" s="10" t="s">
+        <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" t="s">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A4" s="6">
         <v>3</v>
       </c>
-      <c r="C3" t="s">
+      <c r="B4" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" s="7"/>
+      <c r="F4" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H4" s="6"/>
+      <c r="I4" s="6">
+        <v>820000003</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="K4" s="9">
         <v>5</v>
       </c>
-      <c r="D3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" t="s">
-        <v>13</v>
+      <c r="L4" s="6"/>
+      <c r="M4" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="N4" s="10" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
